--- a/output_data/charts/M010000US001.xlsx
+++ b/output_data/charts/M010000US001.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2.735347983254185</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>4.407912474162636</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.505979210858111</c:v>
+                  <c:v>4.506505006470949</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.627320130631247</c:v>
+                  <c:v>4.627421896727543</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.781357922690334</c:v>
+                  <c:v>4.861876737850721</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.914064745466837</c:v>
+                  <c:v>5.068062497145792</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.32223284050147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>12.97398271001434</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>14.68398532803882</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.72628895899887</c:v>
+                  <c:v>14.72680624100827</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14.94684244625309</c:v>
+                  <c:v>14.94980583624322</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>15.16970859055911</c:v>
+                  <c:v>15.22744271296496</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15.41366695164722</c:v>
+                  <c:v>15.46651190967408</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.68327828593828</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.263742017500337</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>4.168386383834215</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.838607132447591</c:v>
+                  <c:v>4.838742303492661</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.961069448542927</c:v>
+                  <c:v>4.960415314730694</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.123392590668885</c:v>
+                  <c:v>5.155863789675691</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.303199384344445</c:v>
+                  <c:v>5.466378544925936</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.784327579503367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2419957792497308</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2451429084966233</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2419675125277328</c:v>
+                  <c:v>0.2422013197845907</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.242831684506745</c:v>
+                  <c:v>0.2429261559696342</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2412266059551718</c:v>
+                  <c:v>0.2405162930589727</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2392454398030422</c:v>
+                  <c:v>0.2371871838901851</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2331630416819355</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2.040044539661563</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>2.556775630165392</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.607023456935893</c:v>
+                  <c:v>2.606873860875632</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.68153440610096</c:v>
+                  <c:v>2.680798904030572</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.742708414831115</c:v>
+                  <c:v>2.737098290202025</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.799679813579628</c:v>
+                  <c:v>2.788212334461007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.8265779521411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>78.74488697031985</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>73.9377972753023</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>73.0801337282318</c:v>
+                  <c:v>73.07887126836789</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>72.54040188396503</c:v>
+                  <c:v>72.53863189229834</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>71.94160587529539</c:v>
+                  <c:v>71.77720217624763</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>71.33014366515883</c:v>
+                  <c:v>70.973647529903</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>70.15042030023383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>4.505979210858111</v>
+        <v>4.506505006470949</v>
       </c>
       <c r="C12" s="2">
-        <v>14.72628895899887</v>
+        <v>14.72680624100827</v>
       </c>
       <c r="D12" s="2">
-        <v>4.838607132447591</v>
+        <v>4.838742303492661</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2419675125277328</v>
+        <v>0.2422013197845907</v>
       </c>
       <c r="F12" s="2">
-        <v>2.607023456935893</v>
+        <v>2.606873860875632</v>
       </c>
       <c r="G12" s="2">
-        <v>73.0801337282318</v>
+        <v>73.07887126836789</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>4.627320130631247</v>
+        <v>4.627421896727543</v>
       </c>
       <c r="C13" s="2">
-        <v>14.94684244625309</v>
+        <v>14.94980583624322</v>
       </c>
       <c r="D13" s="2">
-        <v>4.961069448542927</v>
+        <v>4.960415314730694</v>
       </c>
       <c r="E13" s="2">
-        <v>0.242831684506745</v>
+        <v>0.2429261559696342</v>
       </c>
       <c r="F13" s="2">
-        <v>2.68153440610096</v>
+        <v>2.680798904030572</v>
       </c>
       <c r="G13" s="2">
-        <v>72.54040188396503</v>
+        <v>72.53863189229834</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>4.781357922690334</v>
+        <v>4.861876737850721</v>
       </c>
       <c r="C14" s="2">
-        <v>15.16970859055911</v>
+        <v>15.22744271296496</v>
       </c>
       <c r="D14" s="2">
-        <v>5.123392590668885</v>
+        <v>5.155863789675691</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2412266059551718</v>
+        <v>0.2405162930589727</v>
       </c>
       <c r="F14" s="2">
-        <v>2.742708414831115</v>
+        <v>2.737098290202025</v>
       </c>
       <c r="G14" s="2">
-        <v>71.94160587529539</v>
+        <v>71.77720217624763</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>4.914064745466837</v>
+        <v>5.068062497145792</v>
       </c>
       <c r="C15" s="2">
-        <v>15.41366695164722</v>
+        <v>15.46651190967408</v>
       </c>
       <c r="D15" s="2">
-        <v>5.303199384344445</v>
+        <v>5.466378544925936</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2392454398030422</v>
+        <v>0.2371871838901851</v>
       </c>
       <c r="F15" s="2">
-        <v>2.799679813579628</v>
+        <v>2.788212334461007</v>
       </c>
       <c r="G15" s="2">
-        <v>71.33014366515883</v>
+        <v>70.973647529903</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5.32223284050147</v>
+      </c>
+      <c r="C16" s="2">
+        <v>15.68327828593828</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5.784327579503367</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2331630416819355</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.8265779521411</v>
+      </c>
+      <c r="G16" s="2">
+        <v>70.15042030023383</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/M010000US001.xlsx
+++ b/output_data/charts/M010000US001.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.735347983254185</c:v>
+                  <c:v>2.734628120299858</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.850877093597287</c:v>
+                  <c:v>2.845907452824673</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.967983918965962</c:v>
+                  <c:v>2.959429266405693</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.145791119505174</c:v>
+                  <c:v>3.133140488712374</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.346409390204972</c:v>
+                  <c:v>3.328502169637013</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.579246821280508</c:v>
+                  <c:v>3.556277685462773</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.808946007394437</c:v>
+                  <c:v>3.768610355252887</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.034783227259197</c:v>
+                  <c:v>3.979771700719474</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.218483552486687</c:v>
+                  <c:v>4.152720587309382</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.407912474162636</c:v>
+                  <c:v>4.307764598848014</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>4.506505006470949</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>12.97398271001434</c:v>
+                  <c:v>12.97402697770089</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.12030686832697</c:v>
+                  <c:v>13.12125191101265</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.30521398331256</c:v>
+                  <c:v>13.30781703565557</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.48479636382198</c:v>
+                  <c:v>13.48889663424716</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.69179795343486</c:v>
+                  <c:v>13.69678774405126</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.89126437579143</c:v>
+                  <c:v>13.89941472769002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.09945891118909</c:v>
+                  <c:v>14.10806392199257</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14.32616918313106</c:v>
+                  <c:v>14.32404260908621</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>14.51878202613899</c:v>
+                  <c:v>14.48973509794786</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14.68398532803882</c:v>
+                  <c:v>14.61982238229672</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>14.72680624100827</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>3.263742017500337</c:v>
+                  <c:v>3.263902131409399</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.331038649039745</c:v>
+                  <c:v>3.330249726803944</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.405855203315029</c:v>
+                  <c:v>3.405792250491628</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.493252075644221</c:v>
+                  <c:v>3.493225648186587</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.582585253084406</c:v>
+                  <c:v>3.583629724641216</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.679768946555881</c:v>
+                  <c:v>3.681835733282428</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.78839398610958</c:v>
+                  <c:v>3.791150147646374</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.914108107123939</c:v>
+                  <c:v>3.911425980695406</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.036420917067113</c:v>
+                  <c:v>4.02196953479489</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.168386383834215</c:v>
+                  <c:v>4.128305650082543</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>4.838742303492661</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2419957792497308</c:v>
+                  <c:v>0.2419094106419105</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2410551499196256</c:v>
+                  <c:v>0.241763212558996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2431919504991634</c:v>
+                  <c:v>0.243870989191591</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2453709971303844</c:v>
+                  <c:v>0.245843591616365</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2438057552190218</c:v>
+                  <c:v>0.2441170638924323</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2428923311766032</c:v>
+                  <c:v>0.2433066800872919</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2433204858171746</c:v>
+                  <c:v>0.2436873554769978</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2435943740835572</c:v>
+                  <c:v>0.2441887070667695</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2447358099165406</c:v>
+                  <c:v>0.2453418625833722</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2451429084966233</c:v>
+                  <c:v>0.2448189976542866</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.2422013197845907</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.040044539661563</c:v>
+                  <c:v>2.038807025341955</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.101199656114593</c:v>
+                  <c:v>2.095553125131726</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.146952801266719</c:v>
+                  <c:v>2.136521927048069</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.214997014978373</c:v>
+                  <c:v>2.201536688948138</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.266165724769612</c:v>
+                  <c:v>2.249079242197466</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.325929330951101</c:v>
+                  <c:v>2.303820973487034</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.390341665554684</c:v>
+                  <c:v>2.36521848142764</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.441786957178963</c:v>
+                  <c:v>2.413158987483369</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.49786579802374</c:v>
+                  <c:v>2.463114771301088</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.556775630165392</c:v>
+                  <c:v>2.51954865324557</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.606873860875632</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>78.74488697031985</c:v>
+                  <c:v>78.74672633460598</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>78.35552258300179</c:v>
+                  <c:v>78.36527457166802</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77.93080214264056</c:v>
+                  <c:v>77.94656853120745</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77.41579242891986</c:v>
+                  <c:v>77.43735694828938</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76.86923592328714</c:v>
+                  <c:v>76.89788405558062</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.28089819424449</c:v>
+                  <c:v>76.31534419999045</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75.66953894393504</c:v>
+                  <c:v>75.72326973820354</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>75.03955815122329</c:v>
+                  <c:v>75.12741201494877</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>74.48371189636693</c:v>
+                  <c:v>74.62711814606341</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.9377972753023</c:v>
+                  <c:v>74.17973971787288</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>73.07887126836789</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>2.735347983254185</v>
+        <v>2.734628120299858</v>
       </c>
       <c r="C2" s="2">
-        <v>12.97398271001434</v>
+        <v>12.97402697770089</v>
       </c>
       <c r="D2" s="2">
-        <v>3.263742017500337</v>
+        <v>3.263902131409399</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2419957792497308</v>
+        <v>0.2419094106419105</v>
       </c>
       <c r="F2" s="2">
-        <v>2.040044539661563</v>
+        <v>2.038807025341955</v>
       </c>
       <c r="G2" s="2">
-        <v>78.74488697031985</v>
+        <v>78.74672633460598</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>2.850877093597287</v>
+        <v>2.845907452824673</v>
       </c>
       <c r="C3" s="2">
-        <v>13.12030686832697</v>
+        <v>13.12125191101265</v>
       </c>
       <c r="D3" s="2">
-        <v>3.331038649039745</v>
+        <v>3.330249726803944</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2410551499196256</v>
+        <v>0.241763212558996</v>
       </c>
       <c r="F3" s="2">
-        <v>2.101199656114593</v>
+        <v>2.095553125131726</v>
       </c>
       <c r="G3" s="2">
-        <v>78.35552258300179</v>
+        <v>78.36527457166802</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>2.967983918965962</v>
+        <v>2.959429266405693</v>
       </c>
       <c r="C4" s="2">
-        <v>13.30521398331256</v>
+        <v>13.30781703565557</v>
       </c>
       <c r="D4" s="2">
-        <v>3.405855203315029</v>
+        <v>3.405792250491628</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2431919504991634</v>
+        <v>0.243870989191591</v>
       </c>
       <c r="F4" s="2">
-        <v>2.146952801266719</v>
+        <v>2.136521927048069</v>
       </c>
       <c r="G4" s="2">
-        <v>77.93080214264056</v>
+        <v>77.94656853120745</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>3.145791119505174</v>
+        <v>3.133140488712374</v>
       </c>
       <c r="C5" s="2">
-        <v>13.48479636382198</v>
+        <v>13.48889663424716</v>
       </c>
       <c r="D5" s="2">
-        <v>3.493252075644221</v>
+        <v>3.493225648186587</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2453709971303844</v>
+        <v>0.245843591616365</v>
       </c>
       <c r="F5" s="2">
-        <v>2.214997014978373</v>
+        <v>2.201536688948138</v>
       </c>
       <c r="G5" s="2">
-        <v>77.41579242891986</v>
+        <v>77.43735694828938</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>3.346409390204972</v>
+        <v>3.328502169637013</v>
       </c>
       <c r="C6" s="2">
-        <v>13.69179795343486</v>
+        <v>13.69678774405126</v>
       </c>
       <c r="D6" s="2">
-        <v>3.582585253084406</v>
+        <v>3.583629724641216</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2438057552190218</v>
+        <v>0.2441170638924323</v>
       </c>
       <c r="F6" s="2">
-        <v>2.266165724769612</v>
+        <v>2.249079242197466</v>
       </c>
       <c r="G6" s="2">
-        <v>76.86923592328714</v>
+        <v>76.89788405558062</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>3.579246821280508</v>
+        <v>3.556277685462773</v>
       </c>
       <c r="C7" s="2">
-        <v>13.89126437579143</v>
+        <v>13.89941472769002</v>
       </c>
       <c r="D7" s="2">
-        <v>3.679768946555881</v>
+        <v>3.681835733282428</v>
       </c>
       <c r="E7" s="2">
-        <v>0.2428923311766032</v>
+        <v>0.2433066800872919</v>
       </c>
       <c r="F7" s="2">
-        <v>2.325929330951101</v>
+        <v>2.303820973487034</v>
       </c>
       <c r="G7" s="2">
-        <v>76.28089819424449</v>
+        <v>76.31534419999045</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>3.808946007394437</v>
+        <v>3.768610355252887</v>
       </c>
       <c r="C8" s="2">
-        <v>14.09945891118909</v>
+        <v>14.10806392199257</v>
       </c>
       <c r="D8" s="2">
-        <v>3.78839398610958</v>
+        <v>3.791150147646374</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2433204858171746</v>
+        <v>0.2436873554769978</v>
       </c>
       <c r="F8" s="2">
-        <v>2.390341665554684</v>
+        <v>2.36521848142764</v>
       </c>
       <c r="G8" s="2">
-        <v>75.66953894393504</v>
+        <v>75.72326973820354</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>4.034783227259197</v>
+        <v>3.979771700719474</v>
       </c>
       <c r="C9" s="2">
-        <v>14.32616918313106</v>
+        <v>14.32404260908621</v>
       </c>
       <c r="D9" s="2">
-        <v>3.914108107123939</v>
+        <v>3.911425980695406</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2435943740835572</v>
+        <v>0.2441887070667695</v>
       </c>
       <c r="F9" s="2">
-        <v>2.441786957178963</v>
+        <v>2.413158987483369</v>
       </c>
       <c r="G9" s="2">
-        <v>75.03955815122329</v>
+        <v>75.12741201494877</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>4.218483552486687</v>
+        <v>4.152720587309382</v>
       </c>
       <c r="C10" s="2">
-        <v>14.51878202613899</v>
+        <v>14.48973509794786</v>
       </c>
       <c r="D10" s="2">
-        <v>4.036420917067113</v>
+        <v>4.02196953479489</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2447358099165406</v>
+        <v>0.2453418625833722</v>
       </c>
       <c r="F10" s="2">
-        <v>2.49786579802374</v>
+        <v>2.463114771301088</v>
       </c>
       <c r="G10" s="2">
-        <v>74.48371189636693</v>
+        <v>74.62711814606341</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>4.407912474162636</v>
+        <v>4.307764598848014</v>
       </c>
       <c r="C11" s="2">
-        <v>14.68398532803882</v>
+        <v>14.61982238229672</v>
       </c>
       <c r="D11" s="2">
-        <v>4.168386383834215</v>
+        <v>4.128305650082543</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2451429084966233</v>
+        <v>0.2448189976542866</v>
       </c>
       <c r="F11" s="2">
-        <v>2.556775630165392</v>
+        <v>2.51954865324557</v>
       </c>
       <c r="G11" s="2">
-        <v>73.9377972753023</v>
+        <v>74.17973971787288</v>
       </c>
     </row>
     <row r="12" spans="1:7">
